--- a/issue_log.xlsx
+++ b/issue_log.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L28"/>
+  <dimension ref="A1:L29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2197,6 +2197,69 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Storybook preview.tsx wrapper decorator 가 dark:[#131722]/[#d1d4dc] 하드코딩 (토큰 마이그레이션 누락)</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Storybook 다크모드 전환</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>1. apps/docs/.storybook/preview.tsx 의 Story wrapper 가 dark:bg-[#131722] dark:text-[#d1d4dc] 사용
+2. v0.1.0 토큰 마이그레이션 시 컴포넌트만 grep 해서 docs preview decorator 누락
+3. 다크 토큰 시스템 일관성 깨짐</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>원인: Codex 가 packages/ui/src/components/ 만 검사하고 apps/docs 는 범위 외였음.
+수정: bg-background text-foreground 토큰으로 교체, 주석도 갱신.</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>apps/docs/.storybook (라이브러리 출판물에는 영향 없음)</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>@sym/ui 0.1.0 (docs decorator 잔존)</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>docs 0.0.0 (post-v0.1.0)</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/issue_log.xlsx
+++ b/issue_log.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L29"/>
+  <dimension ref="A1:L40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2260,6 +2260,638 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>CLI init 이 토큰 CSS 변수와 Tailwind preset 을 주입하지 않음</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>@sym/ui-cli@0.1.0 으로 init 후 add 한 컴포넌트를 소비 프로젝트에서 렌더링</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>1) sym-ui init 실행 2) sym-ui add button 3) &lt;Button /&gt; 렌더 4) bg-background, bg-primary 가 적용되지 않음</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>init.ts 의 GLOBALS_CSS 가 폰트와 Tailwind 지시문만 포함, --background 등 시맨틱 토큰 누락. 또한 tailwind preset 은 경고만 출력하고 자동 패치 미수행. 수정: build-registry 가 templates/globals.css 를 registry.json 의 globalsCss 필드로 임베드 후 init 이 prepend, .cjs/.js 에 한해 regex 기반 preset 자동 patch.</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>CLI 로 설치한 모든 소비 프로젝트의 토큰 기반 스타일링</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>@sym/ui-cli 0.1.0</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>@sym/ui-cli 0.2.0 (commit: pending)</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>CLI add 가 internalDeps 를 재귀 복사하지 않음</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>combobox/form/date-picker 같이 다른 컴포넌트에 의존하는 컴포넌트 설치</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>1) sym-ui add combobox 2) 소비 프로젝트에서 import 시 popover/command/button 모듈 not found, 컴파일 실패</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>add.ts 가 요청한 단일 컴포넌트만 복사하고 internalDeps 무시. 수정: resolveDependencyClosure() BFS 로 internalDeps 그래프 순회, ordered list 로 누락 없이 복사. utils 는 init 이 처리하므로 SKIP. npm 의존성도 종속분 통합 install.</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>CLI 로 합성 컴포넌트 (combobox, form, date-picker, number-input, pagination, file-upload) 를 설치한 소비 프로젝트</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>@sym/ui-cli 0.1.0</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>@sym/ui-cli 0.2.0 (commit: pending)</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>CLI init 의 Tailwind preset 자동 패치</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>기존 init 은 preset 미적용 시 경고만 출력. 수정: tailwind.config 의 presets 배열에 @sym/ui/tailwind.preset 을 자동 주입 (.cjs/.js 두 가지 전략, .ts/.mjs 는 명확한 수동 안내).</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>shadcn 식 CLI 의 사용자 경험 개선. 수동 단계가 줄어 init 한 번으로 사용 가능.</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>CLI 로 설치하는 모든 소비 프로젝트</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>@sym/ui-cli 0.1.0</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>@sym/ui-cli 0.2.0 (commit: pending)</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>컴포넌트 카탈로그 26 → 36 확장 (Tier 4 신규 10종)</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Separator, Alert (status/alert role 자동 분기), Breadcrumb, Pagination, Slider (단일/range thumb 자동), NumberInput, Drawer (Sheet bottom 변형), Stepper, EmptyState, FileUpload (button role + drag&amp;drop) 추가. 각각 .tsx + .test.tsx + stories. 의존성 @radix-ui/react-separator, @radix-ui/react-slider 추가.</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>shadcn/ui 40+, MUI 80+ 와의 갭 축소. 종합 평가에서 카탈로그 부족이 약점으로 지적됨.</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>@sym/ui 라이브러리 카탈로그 전반</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>@sym/ui 0.1.0</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>@sym/ui 0.2.0 (commit: pending)</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>모션 토큰 도입 (duration + easing)</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>duration (instant/fast 150/base 200/slow 300/slower 500) + easing (standard/decelerate/accelerate/emphasized) 토큰 신설. Tailwind preset 의 transitionDuration / transitionTimingFunction 으로 노출.</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>이전엔 accordion 키프레임만 존재해 컴포넌트 간 모션 일관성을 보장할 수 없었음. 종합 평가의 약점 지적.</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>전 컴포넌트의 모션 일관성</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>@sym/ui 0.1.0</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>@sym/ui 0.2.0 (commit: pending)</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Storybook test-runner + axe 기반 a11y 자동 검증 CI 게이트</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>@storybook/test-runner + axe-playwright 도입. CI 에 a11y job 추가 (storybook 빌드 → playwright chromium → 모든 stories 의 WCAG 2.1 AA 자동 검증). landmark scope 의 region 룰만 stories 에 부적합으로 비활성.</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Codex 1차 검토에서 'Radix 기반이라 기본 접근성은 괜찮지만 WCAG AA 를 검증한다고 보기엔 부족' 지적.</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>전 컴포넌트의 접근성 회귀 차단</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>전체 0.1.0</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>전체 0.2.0 (commit: pending)</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>README 정체성/카탈로그/모션 토큰/a11y 자동화 명시 재작성</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>README 상단에 shadcn 식 소스 복사 모델임을 명시, @sym/ui 는 private:true (npm 미배포) 와 @sym/ui-cli 만 배포 분리 명확화. 36개 카탈로그, 모션 토큰, a11y 자동화 반영.</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Codex 1차 검토 5번 (스펙/구현 불일치) 의 절반. 사용자가 'shadcn 식인지 npm 패키지 모델인지' 혼란을 겪지 않도록.</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>신규 사용자 onboarding</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>전체 0.1.0</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>전체 0.2.0 (commit: pending)</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>설계 스펙 문서를 Draft / Future Plan 으로 명시 + 현재 구현과의 차이 표 추가</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>docs/superpowers/specs/2026-04-24-design-system-design.md 의 헤더에 Draft / Future Plan 명시, Button loading prop / Label hint / --color-primary-500 명명 / Chromatic / Husky 등이 현재 구현에 없음을 표로 명시.</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Codex 1차 검토 5번 (스펙/구현 불일치) 의 잔여. 미래 개선 방향을 보존하면서 혼란 방지.</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>기여자 / 미래의 자기 자신</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>전체 0.1.0</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>전체 0.2.0 (commit: pending)</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>asChild 패턴 일관성: Card, Badge 에 추가</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>기존 Button 만 지원하던 asChild 를 Card (Link 로 감쌀 때) 와 Badge (NavLink 등) 에도 노출. Trigger 계열은 Radix Primitive 의 asChild 가 자동 통과되므로 별도 작업 불필요.</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>종합 평가에서 'shadcn/ui 의 핵심 가치 중 하나를 빠뜨린 셈' 지적. Link 로 감싸는 일반 패턴 지원 강화.</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Card, Badge 컴포넌트 사용처</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>@sym/ui 0.1.0</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>@sym/ui 0.2.0 (commit: pending)</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>CLI findConfigFile 의 tailwind.config 후보에 .cjs 누락</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>tailwind.config.cjs 만 존재하는 프로젝트에서 sym-ui init 실행</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>1) tailwind.config.cjs 만 있는 프로젝트에서 sym-ui init 2) 'tailwind.config 가 없습니다' 오류로 종료</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>init.ts 의 findConfigFile 후보가 .ts/.js/.mjs 만 검사. 수정: .cjs 추가.</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>tailwind.config.cjs 사용 프로젝트의 init</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>@sym/ui-cli 0.1.0</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>@sym/ui-cli 0.2.0 (commit: pending)</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Slider 가 thumb 1개만 렌더해 range 모드 동작 불가</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>v0.2.0 신규 Slider 컴포넌트에 defaultValue 가 [a, b] 형태로 전달</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>1) &lt;Slider defaultValue={[20, 80]} max={100} /&gt; 렌더 2) thumb 이 1개만 표시되어 range 조작 불가</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Slider 컴포넌트가 SliderPrimitive.Thumb 을 단일로 렌더. 수정: defaultValue/value 의 length 만큼 동적 렌더 (Array.from({length: thumbCount}).map).</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Slider 컴포넌트의 range 모드</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>@sym/ui 0.2.0 개발 중 발견</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>@sym/ui 0.2.0 (commit: pending)</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/issue_log.xlsx
+++ b/issue_log.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L40"/>
+  <dimension ref="A1:L57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2399,7 +2399,6 @@
           <t>CLI init 의 Tailwind preset 자동 패치</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
           <t>기존 init 은 preset 미적용 시 경고만 출력. 수정: tailwind.config 의 presets 배열에 @sym/ui/tailwind.preset 을 자동 주입 (.cjs/.js 두 가지 전략, .ts/.mjs 는 명확한 수동 안내).</t>
@@ -2455,7 +2454,6 @@
           <t>컴포넌트 카탈로그 26 → 36 확장 (Tier 4 신규 10종)</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
           <t>Separator, Alert (status/alert role 자동 분기), Breadcrumb, Pagination, Slider (단일/range thumb 자동), NumberInput, Drawer (Sheet bottom 변형), Stepper, EmptyState, FileUpload (button role + drag&amp;drop) 추가. 각각 .tsx + .test.tsx + stories. 의존성 @radix-ui/react-separator, @radix-ui/react-slider 추가.</t>
@@ -2511,7 +2509,6 @@
           <t>모션 토큰 도입 (duration + easing)</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
           <t>duration (instant/fast 150/base 200/slow 300/slower 500) + easing (standard/decelerate/accelerate/emphasized) 토큰 신설. Tailwind preset 의 transitionDuration / transitionTimingFunction 으로 노출.</t>
@@ -2567,7 +2564,6 @@
           <t>Storybook test-runner + axe 기반 a11y 자동 검증 CI 게이트</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
           <t>@storybook/test-runner + axe-playwright 도입. CI 에 a11y job 추가 (storybook 빌드 → playwright chromium → 모든 stories 의 WCAG 2.1 AA 자동 검증). landmark scope 의 region 룰만 stories 에 부적합으로 비활성.</t>
@@ -2623,7 +2619,6 @@
           <t>README 정체성/카탈로그/모션 토큰/a11y 자동화 명시 재작성</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
           <t>README 상단에 shadcn 식 소스 복사 모델임을 명시, @sym/ui 는 private:true (npm 미배포) 와 @sym/ui-cli 만 배포 분리 명확화. 36개 카탈로그, 모션 토큰, a11y 자동화 반영.</t>
@@ -2679,7 +2674,6 @@
           <t>설계 스펙 문서를 Draft / Future Plan 으로 명시 + 현재 구현과의 차이 표 추가</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
           <t>docs/superpowers/specs/2026-04-24-design-system-design.md 의 헤더에 Draft / Future Plan 명시, Button loading prop / Label hint / --color-primary-500 명명 / Chromatic / Husky 등이 현재 구현에 없음을 표로 명시.</t>
@@ -2735,7 +2729,6 @@
           <t>asChild 패턴 일관성: Card, Badge 에 추가</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
           <t>기존 Button 만 지원하던 asChild 를 Card (Link 로 감쌀 때) 와 Badge (NavLink 등) 에도 노출. Trigger 계열은 Radix Primitive 의 asChild 가 자동 통과되므로 별도 작업 불필요.</t>
@@ -2889,6 +2882,1002 @@
       <c r="L40" t="inlineStr">
         <is>
           <t>Major</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>fix(cli): add 가 missing dep 발견 후에도 부모 컴포넌트를 계속 push</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>registry 에 없는 컴포넌트가 internalDeps 에 포함된 경우</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>1) registry 오타 또는 동기화 누락으로 누락된 dep 가 있는 부모 컴포넌트 add 시도 2) missing 출력 후 부모 컴포넌트는 그대로 ordered 에 들어가 깨진 상태로 설치됨</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>add.ts 의 resolveDependencyClosure 가 missing 만 push 하고 부모는 ordered 에 그대로 push. 수정: missing.length &gt; 0 이면 process.exit(1) 로 즉시 abort + 메시지 출력. missing 도 Set 으로 변경해 중복 출력 방지.</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>registry 동기화가 어긋났을 때의 CLI 안전성</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>@sym/ui-cli 0.2.0</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>@sym/ui-cli 0.2.1 (commit: pending)</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>docs(cli): resolveDependencyClosure 알고리즘 코멘트 정정 (BFS -&gt; DFS post-order)</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>코드는 DFS post-order (자식 먼저 ordered 에 push) 인데 코멘트와 RELEASE_NOTES 표기가 BFS 였음. 수정: 코멘트 정정.</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Codex 검증에서 알고리즘 표기 불일치 지적. 코드와 문서 정합성 확보.</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>기여자/리뷰어</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>@sym/ui-cli 0.2.0</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>@sym/ui-cli 0.2.1 (commit: pending)</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>fix(cli): init 의 globals.css 토큰 존재 검사가 false-positive 가능</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>기존 globals.css 에 --background-color 같은 다른 변수만 있는 경우</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>1) 기존 globals.css 에 주석이나 --background-color 변수만 있음 2) init 실행 3) sym-ui 토큰 주입을 잘못 스킵 -&gt; 컴포넌트 렌더 깨짐</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>init.ts 가 existing.includes(--background) 로만 검사. 수정: (^|[;{]\s*)--background\s*: 정규식으로 실제 custom property 선언만 매칭.</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>기존 CSS 가 있는 프로젝트의 init 정확성</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>@sym/ui-cli 0.2.0</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>@sym/ui-cli 0.2.1 (commit: pending)</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>fix(cli): init 이 Tailwind 지시문을 중복 주입할 수 있음</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>기존 globals.css 에 @tailwind base 등 지시문이 이미 있는 경우</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>1) 사용자가 Tailwind 를 직접 설정한 globals.css 에 @tailwind base; 등이 있음 2) sym-ui 토큰은 없음 3) init 이 sym-ui template 전체를 prepend -&gt; @tailwind 지시문 중복</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>init.ts 가 토큰 부재 시 sym-ui template 전체 (지시문 포함) 를 prepend. 수정: extractTokenLayer() 로 @layer base 블록만 추출, 지시문이 이미 있으면 토큰 layer 만 주입.</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>기존 Tailwind 설정이 있는 프로젝트의 init</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>@sym/ui-cli 0.2.0</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>@sym/ui-cli 0.2.1 (commit: pending)</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>fix(cli): tailwind preset regex 가 다중 presets 매치 시 잘못된 위치 패치 가능</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>tailwind.config.cjs 안에 nested 객체에도 presets 배열이 있는 경우</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>1) plugin 옵션 객체 안에 또 다른 presets: 배열이 있는 tailwind.config 2) init 의 자동 patch 가 첫 매치만 잡아 nested 위치를 잘못 수정</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>init.ts 의 단일 regex 매치가 안전하지 않음. 수정: presets 매치 카운트가 2 이상이면 manual-needed-multiple-presets 로 폴백, 명확한 안내.</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>비표준 tailwind.config 구조</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>@sym/ui-cli 0.2.0</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>@sym/ui-cli 0.2.1 (commit: pending)</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>fix(cli): .js 파일이 ESM (type:module) 일 때 require() 자동 삽입 위험</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>package.json 에 type:module 이고 tailwind.config.js 사용</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>1) Next.js 14+ 등 type:module 프로젝트 2) tailwind.config.js (ESM) 에 init 이 require(@sym/ui/tailwind.preset) 자동 삽입 3) 런타임 폭발</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>init.ts 가 .cjs/.js 를 모두 CommonJS 로 가정. 수정: detectPackageType() 로 package.json type 감지, .js + module 조합은 manual-needed-esm-js 로 폴백.</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>ESM 프로젝트의 init</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>@sym/ui-cli 0.2.0</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>@sym/ui-cli 0.2.1 (commit: pending)</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>fix(ui): Stepper 가 Fragment 안의 StepperItem 에 index 를 부여하지 못함</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Stepper children 에 Fragment 또는 조건부 렌더링이 끼어 있는 경우</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>1) Stepper 안에 React.Fragment 안에 StepperItem 두 개가 있는 형태 2) 두 StepperItem 모두 index=0 으로 cloneElement 되어 status 가 어긋남</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>React.Children.map 이 Fragment 안의 children 까지 펼치지 않음. 수정: flattenChildren() 으로 Fragment 재귀 펼침 + displayName 기반 StepperItem 필터링 후 인덱스 부여.</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Stepper 의 children 배치 자유도</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>@sym/ui 0.2.0</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>@sym/ui 0.2.1 (commit: pending)</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>fix(ui): FileUpload 의 button-in-button 중첩</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>FileUpload 컴포넌트 사용 시</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>1) FileUpload 렌더 2) DOM 구조에 div role=button 안에 native button (파일 선택) 이 있음 3) 키보드 진입점 두 개, a11y 충돌</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>내부 어포던스를 native Button 으로 렌더. 수정: span + buttonVariants 클래스 + aria-hidden + pointer-events-none 으로 시각용 표시만 유지.</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>FileUpload 의 키보드 접근성</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>@sym/ui 0.2.0</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>@sym/ui 0.2.1 (commit: pending)</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>feat(ui): Slider 다중 thumb 의 aria-label 지정 API 추가</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>다중 thumb (range) 모드에서 thumb 별 aria-label 부여 API 부재. 수정: thumbAriaLabels?: string[] 노출, Thumb 렌더 시 aria-label={thumbAriaLabels?.[i]}.</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Codex 지적: range slider 는 thumb 별 라벨이 권장 패턴. 사용자에게 옵션 제공.</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Slider 의 range 모드 a11y</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>@sym/ui 0.2.0</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>@sym/ui 0.2.1 (commit: pending)</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>fix(ui): Pagination Ellipsis 가 부모 aria-hidden 으로 sr-only 텍스트까지 숨김</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Pagination 안에 PaginationEllipsis 사용</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>1) PaginationEllipsis 렌더 2) wrapper span 자체에 aria-hidden 이 있어 내부 sr-only More pages 도 함께 숨겨짐 3) 스크린 리더가 ellipsis 의미를 못 받음</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>wrapper 의 aria-hidden 을 글리프로 분리. 수정: 시각용 글리프만 aria-hidden, sr-only 텍스트는 노출.</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Pagination 의 스크린 리더 사용성</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>@sym/ui 0.2.0</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>@sym/ui 0.2.1 (commit: pending)</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>fix(ui): Breadcrumb 현재 페이지에 role=link + aria-disabled 부여</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Breadcrumb 의 BreadcrumbPage 사용</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>1) BreadcrumbPage 렌더 2) span 에 role=link aria-disabled=true 가 부여되어 비활성 링크처럼 노출</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>현재 페이지는 링크가 아니므로 link role 부적절. 수정: role/aria-disabled 제거, span + aria-current=page 만으로 의미 전달.</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Breadcrumb 의 의미 정확성</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>@sym/ui 0.2.0</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>@sym/ui 0.2.1 (commit: pending)</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>fix(ui): Alert AlertDescription 의 ref 타입 미스매치</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>AlertDescription 에 ref 를 attach 하는 경우</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>1) ref 를 HTMLParagraphElement 로 선언 2) AlertDescription 에 attach 3) 실제 렌더는 div 라 ref.current 는 HTMLDivElement 이지만 타입은 HTMLParagraphElement 로 미스매치</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>forwardRef 제네릭 타입이 잘못 선언. 수정: HTMLDivElement 로 통일 + props 도 HTMLAttributes&lt;HTMLDivElement&gt;.</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Alert 의 ref 사용처</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>@sym/ui 0.2.0</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>@sym/ui 0.2.1 (commit: pending)</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>docs(ui): Card asChild 사용 시 ref 타입 caveat 명시</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>asChild 로 자식 요소 (a, button 등) 가 div 가 아닐 때 ref 타입 (HTMLDivElement 고정) 과 미스매치 가능. shadcn/ui 와 동일한 약속이라 cast 가이드를 JSDoc 에 명시.</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Codex 지적: polymorphic 패턴 미적용으로 인한 ref 타입 caveat 가 명시 필요.</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Card 의 asChild 사용처</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>@sym/ui 0.2.0</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>@sym/ui 0.2.1 (commit: pending)</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>docs(ui): Badge asChild 사용 시 ref 타입 caveat 명시</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Card 와 동일 사유. JSDoc 에 caveat 추가.</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Codex 지적 동일.</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Badge 의 asChild 사용처</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>@sym/ui 0.2.0</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>@sym/ui 0.2.1 (commit: pending)</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>bug</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>fix(ui): NumberInput onChange 가 null 을 내보내지만 value 는 number | undefined 만 허용</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>NumberInput 을 controlled 로 사용</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>1) state 를 number | undefined 로 선언 2) NumberInput value/onChange 연결 3) onChange 가 number | null 을 내보내 setState 시그니처 미스매치</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>내부 상태와 콜백을 number | undefined 로 통일. 수정: onChange?: (value: number | undefined) =&gt; void, internal state 도 number | undefined.</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>NumberInput 의 controlled 사용처 (storybook 포함)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>@sym/ui 0.2.0</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>@sym/ui 0.2.1 (commit: pending)</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>docs(ui): motion 토큰 의도 (Material 2 / Tailwind 호환) 주석 보강</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>easing 곡선이 Material 2 + Tailwind 기본값 호환 의도임을 motion.ts 코멘트에 명시. M3 의 standard 곡선은 본 토큰의 emphasized 와 매핑됨을 안내. M3 가 필요하면 Tailwind preset override 가능.</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Codex 지적: 이름이 Material 2 / Tailwind 와 가깝지만 M3 와 다름. 의도 명확화로 사용자 혼란 방지.</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>motion 토큰 사용자/기여자</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>@sym/ui 0.2.0</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>@sym/ui 0.2.1 (commit: pending)</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>feat(ci): a11y test-runner runOnly 에 wcag22aa 추가</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>axe 의 runOnly 태그에 wcag22aa 포함. best-practice 는 noise 가 많아 우선 제외. 단계적 도입.</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Codex 지적: WCAG 2.2 AA 는 추가 권장. 품질 기준 상향.</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>전 컴포넌트의 a11y CI 게이트</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>전체 0.2.0</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>전체 0.2.1 (commit: pending)</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>Minor</t>
         </is>
       </c>
     </row>

--- a/issue_log.xlsx
+++ b/issue_log.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L57"/>
+  <dimension ref="A1:L61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2964,7 +2964,6 @@
           <t>docs(cli): resolveDependencyClosure 알고리즘 코멘트 정정 (BFS -&gt; DFS post-order)</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
           <t>코드는 DFS post-order (자식 먼저 ordered 에 push) 인데 코멘트와 RELEASE_NOTES 표기가 BFS 였음. 수정: 코멘트 정정.</t>
@@ -3380,7 +3379,6 @@
           <t>feat(ui): Slider 다중 thumb 의 aria-label 지정 API 추가</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
           <t>다중 thumb (range) 모드에서 thumb 별 aria-label 부여 API 부재. 수정: thumbAriaLabels?: string[] 노출, Thumb 렌더 시 aria-label={thumbAriaLabels?.[i]}.</t>
@@ -3616,7 +3614,6 @@
           <t>docs(ui): Card asChild 사용 시 ref 타입 caveat 명시</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
           <t>asChild 로 자식 요소 (a, button 등) 가 div 가 아닐 때 ref 타입 (HTMLDivElement 고정) 과 미스매치 가능. shadcn/ui 와 동일한 약속이라 cast 가이드를 JSDoc 에 명시.</t>
@@ -3672,7 +3669,6 @@
           <t>docs(ui): Badge asChild 사용 시 ref 타입 caveat 명시</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
           <t>Card 와 동일 사유. JSDoc 에 caveat 추가.</t>
@@ -3788,7 +3784,6 @@
           <t>docs(ui): motion 토큰 의도 (Material 2 / Tailwind 호환) 주석 보강</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
           <t>easing 곡선이 Material 2 + Tailwind 기본값 호환 의도임을 motion.ts 코멘트에 명시. M3 의 standard 곡선은 본 토큰의 emphasized 와 매핑됨을 안내. M3 가 필요하면 Tailwind preset override 가능.</t>
@@ -3844,7 +3839,6 @@
           <t>feat(ci): a11y test-runner runOnly 에 wcag22aa 추가</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
           <t>axe 의 runOnly 태그에 wcag22aa 포함. best-practice 는 noise 가 많아 우선 제외. 단계적 도입.</t>
@@ -3876,6 +3870,230 @@
         </is>
       </c>
       <c r="L57" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>feat(ui): lucide-react 도입 + 11개 컴포넌트의 텍스트 글리프 교체</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>유니코드 문자 (+, −, ‹, ›, ▾, ▦, ▲, ▼, ↕, …, ⌕, ⬆, ✕, ✓) 로 렌더되던 아이콘을 lucide 의 정식 SVG 아이콘 (Plus, Minus, ChevronLeft/Right/Down, ArrowUp/Down/UpDown, MoreHorizontal, Search, UploadCloud, X, Check, Calendar) 으로 교체. 대상: combobox, date-picker, select, command, file-upload, data-table, pagination, breadcrumb, sheet, stepper, number-input. registry meta dependencies 에 lucide-react 추가.</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Codex 디자인 평가 (7.5/10) 에서 텍스트 글리프 아이콘이 아마추어 인상을 준다는 지적. 일관된 stroke 굵기와 크기로 시각 완성도 상향.</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>11개 컴포넌트의 시각 완성도</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>@sym/ui 0.2.1</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>@sym/ui 0.3.0 (commit: pending)</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>feat(docs): 5개 패턴 스토리 추가 (Patterns/ 카테고리)</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>기존 stories 가 컴포넌트 단품 나열 중심이라 실제 화면 리듬 판단 어려운 약점 해소. Patterns/Settings Page (Tabs+Form+Card+Switch+Select), Empty Search Results (Input+EmptyState), File Upload Form (Card+Alert+FileUpload+Form), DataTable with Filters (Card+Input+Combobox+DataTable+Pagination+EmptyState), Account Activity (Stepper+Card+Badge+Separator) 추가.</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Codex 디자인 평가에서 가장 큰 약점으로 지적됨. 컴포넌트 보다 패턴 스토리가 디자인시스템 수준을 결정.</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Storybook 의 디자인 검토 가능성</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>전체 0.2.1</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>전체 0.3.0 (commit: pending)</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>feat(ui): 브랜드 primary 를 Indigo 로 교체 (Tailwind blue 탈피)</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>light mode --primary 217 91% 60% (blue) -&gt; 243 75% 59% (Indigo 600). dark mode --primary 213 93% 62% -&gt; 234 89% 74% (Indigo 400, L=74). dark primary-foreground 240 25% 12% 로 대비 보강. tailwind.preset.cjs 의 primary.50-950 스케일도 Indigo 로 일괄 교체. tokens/colors.ts 의 primary 객체 동기화.</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Codex 디자인 평가 (7.5/10) 에서 Tailwind blue 그대로 쓰면 brand 식별력이 약하다는 지적. shadcn 식 디폴트 톤에서 차별화.</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>전체 시각 인상 (다크 모드 가시성 포함)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>@sym/ui 0.2.1</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>@sym/ui 0.3.0 (commit: pending)</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>chore(docs): patterns 스토리용 의존성 명시 (lucide-react, react-slot)</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>patterns 스토리에서 lucide 아이콘과 Slot (asChild) 을 직접 사용하므로 apps/docs/package.json 의 devDependencies 에 lucide-react, @radix-ui/react-slot 명시. pnpm strict resolution 환경에서 호이스팅 의존 회피.</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>v0.3.0 의 패턴 스토리 작성 과정에서 발견. 의존성 선언 강화.</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>docs 빌드 안정성</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>docs 0.0.0</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>docs 0.0.0 (commit: pending)</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
         <is>
           <t>Minor</t>
         </is>

--- a/issue_log.xlsx
+++ b/issue_log.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L61"/>
+  <dimension ref="A1:L65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3894,7 +3894,6 @@
           <t>feat(ui): lucide-react 도입 + 11개 컴포넌트의 텍스트 글리프 교체</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
           <t>유니코드 문자 (+, −, ‹, ›, ▾, ▦, ▲, ▼, ↕, …, ⌕, ⬆, ✕, ✓) 로 렌더되던 아이콘을 lucide 의 정식 SVG 아이콘 (Plus, Minus, ChevronLeft/Right/Down, ArrowUp/Down/UpDown, MoreHorizontal, Search, UploadCloud, X, Check, Calendar) 으로 교체. 대상: combobox, date-picker, select, command, file-upload, data-table, pagination, breadcrumb, sheet, stepper, number-input. registry meta dependencies 에 lucide-react 추가.</t>
@@ -3950,7 +3949,6 @@
           <t>feat(docs): 5개 패턴 스토리 추가 (Patterns/ 카테고리)</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
           <t>기존 stories 가 컴포넌트 단품 나열 중심이라 실제 화면 리듬 판단 어려운 약점 해소. Patterns/Settings Page (Tabs+Form+Card+Switch+Select), Empty Search Results (Input+EmptyState), File Upload Form (Card+Alert+FileUpload+Form), DataTable with Filters (Card+Input+Combobox+DataTable+Pagination+EmptyState), Account Activity (Stepper+Card+Badge+Separator) 추가.</t>
@@ -4006,7 +4004,6 @@
           <t>feat(ui): 브랜드 primary 를 Indigo 로 교체 (Tailwind blue 탈피)</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
           <t>light mode --primary 217 91% 60% (blue) -&gt; 243 75% 59% (Indigo 600). dark mode --primary 213 93% 62% -&gt; 234 89% 74% (Indigo 400, L=74). dark primary-foreground 240 25% 12% 로 대비 보강. tailwind.preset.cjs 의 primary.50-950 스케일도 Indigo 로 일괄 교체. tokens/colors.ts 의 primary 객체 동기화.</t>
@@ -4062,7 +4059,6 @@
           <t>chore(docs): patterns 스토리용 의존성 명시 (lucide-react, react-slot)</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
           <t>patterns 스토리에서 lucide 아이콘과 Slot (asChild) 을 직접 사용하므로 apps/docs/package.json 의 devDependencies 에 lucide-react, @radix-ui/react-slot 명시. pnpm strict resolution 환경에서 호이스팅 의존 회피.</t>
@@ -4096,6 +4092,230 @@
       <c r="L61" t="inlineStr">
         <is>
           <t>Minor</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>docs(brand): Identity.mdx 의 블루 표기를 indigo 로 정정</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>v0.3.0 에서 primary 를 indigo 로 바꿨지만 brand 문서가 여전히 '블루 중심', '블루 프라이머리' 로 남아 있던 문서 모순 해소. 다크 배경 L&gt;=15% 규칙 + 변경 이력 추가.</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Codex 디자인 재평가 (8.0/10) 에서 indigo 변경과 문서 불일치 지적.</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>신규 사용자 onboarding / 브랜드 문서 정합성</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>docs 0.0.0 (v0.3.0 기준)</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>docs 0.0.0 (commit: pending)</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>feat(ui): Accordion 의 ▾ → lucide ChevronDown 교체</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>v0.3.0 lucide 일괄 교체에서 누락된 Accordion. AccordionTrigger 의 회전 애니메이션 셀렉터도 [&amp;[data-state=open]&gt;span] 에서 [&amp;[data-state=open]&gt;svg] 로 변경. registry meta dependencies 에 lucide-react 추가.</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Codex 디자인 재평가 지적: 아이콘 전략 통일을 위해 Accordion 도 lucide 로 맞춰야 함.</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Accordion 의 시각 완성도</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>@sym/ui 0.3.0</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>@sym/ui 0.4.0 (commit: pending)</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>feat(ui): Checkbox 의 ✓ → lucide Check 교체</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>v0.3.0 lucide 일괄 교체에서 누락된 Checkbox. CheckboxPrimitive.Indicator 의 자식이 Check className=h-3 w-3 로 변경. registry meta dependencies 에 lucide-react 추가.</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Codex 디자인 재평가 지적 동일 (아이콘 전략 통일).</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Checkbox 의 시각 완성도</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>@sym/ui 0.3.0</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>@sym/ui 0.4.0 (commit: pending)</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>feat(docs): 패턴 스토리 시나리오 확장 (5개 패턴 -&gt; 18개 stories)</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>기존 Default 만 있던 5개 패턴 스토리에 Loading / Error / Empty / Mobile / Success / WithSuggestions / Blocked / Completed 등 운영 상태 변형 추가. Settings Page: Default+Loading+ErrorState+Mobile, Empty Search Results: Default+Loading+WithSuggestions, File Upload Form: Default+Uploading+ValidationError+Success, DataTable with Filters: Default+Loading+Empty+Mobile, Account Activity: InProgress+Completed+Blocked. Skeleton + Alert + Progress + Badge 의 복합 사용 패턴 검토 가능.</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Codex 디자인 재평가에서 가장 큰 약점으로 지적: 패턴 스토리가 happy path 만 보여주는 '앱 화면 샘플' 수준. 실제 운영 화면 평가를 위해 변형 추가.</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Storybook 의 디자인 검토 깊이 (단품 -&gt; happy path -&gt; 운영 상태)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>전체 0.3.0</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>전체 0.4.0 (commit: pending)</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>Major</t>
         </is>
       </c>
     </row>

--- a/issue_log.xlsx
+++ b/issue_log.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L65"/>
+  <dimension ref="A1:L69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4114,7 +4114,6 @@
           <t>docs(brand): Identity.mdx 의 블루 표기를 indigo 로 정정</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
           <t>v0.3.0 에서 primary 를 indigo 로 바꿨지만 brand 문서가 여전히 '블루 중심', '블루 프라이머리' 로 남아 있던 문서 모순 해소. 다크 배경 L&gt;=15% 규칙 + 변경 이력 추가.</t>
@@ -4170,7 +4169,6 @@
           <t>feat(ui): Accordion 의 ▾ → lucide ChevronDown 교체</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
           <t>v0.3.0 lucide 일괄 교체에서 누락된 Accordion. AccordionTrigger 의 회전 애니메이션 셀렉터도 [&amp;[data-state=open]&gt;span] 에서 [&amp;[data-state=open]&gt;svg] 로 변경. registry meta dependencies 에 lucide-react 추가.</t>
@@ -4226,7 +4224,6 @@
           <t>feat(ui): Checkbox 의 ✓ → lucide Check 교체</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
           <t>v0.3.0 lucide 일괄 교체에서 누락된 Checkbox. CheckboxPrimitive.Indicator 의 자식이 Check className=h-3 w-3 로 변경. registry meta dependencies 에 lucide-react 추가.</t>
@@ -4282,7 +4279,6 @@
           <t>feat(docs): 패턴 스토리 시나리오 확장 (5개 패턴 -&gt; 18개 stories)</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
           <t>기존 Default 만 있던 5개 패턴 스토리에 Loading / Error / Empty / Mobile / Success / WithSuggestions / Blocked / Completed 등 운영 상태 변형 추가. Settings Page: Default+Loading+ErrorState+Mobile, Empty Search Results: Default+Loading+WithSuggestions, File Upload Form: Default+Uploading+ValidationError+Success, DataTable with Filters: Default+Loading+Empty+Mobile, Account Activity: InProgress+Completed+Blocked. Skeleton + Alert + Progress + Badge 의 복합 사용 패턴 검토 가능.</t>
@@ -4314,6 +4310,230 @@
         </is>
       </c>
       <c r="L65" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>feat(ui): Brand accent (teal) 토큰 도입</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>indigo primary 의 보조 시그니처로 차분한 teal 추가. light --accent-brand 173 80% 35%, dark 172 66% 58%. Tailwind 노출 accent-brand. tokens/colors.ts 에 accent.brand.light/dark export. 사용 가이드: link hover / badge accent / 서브 헤딩 등 primary 가 아닌 곳에서 brand 정체성 유지.</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Codex 디자인 평가 (8.3/10) 에서 indigo + warm gray 조합도 익숙한 SaaS 팔레트라는 지적. 9점대로 가려면 brand 시그니처가 한 색조 더 필요함.</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>전체 시각 인상 (보조 강조 색 도입)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>@sym/ui 0.4.0</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>@sym/ui 0.5.0 (commit: pending)</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>feat(ui): Intent 토큰 3계층 (status / surface / interactive) 도입</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>primitive + semantic 의 기존 2계층 위에 intent 계층 추가. status (success/warning/danger/info × bg/fg = 8개), surface (subtle/raised = 2개), interactive (hover/active = 2개) + focus-ring 별칭. light/dark 양쪽에 정의. Tailwind 노출 (bg-status-success-bg text-status-success-fg, bg-surface-subtle, bg-interactive-hover). tokens/colors.ts 의 intentTokens 배열로 타입 export.</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Codex 디자인 평가에서 9점대 핵심으로 지적 (토큰의 의미 계층 추가). 컴포넌트 코드의 의도가 토큰 단계에서 드러나도록 시스템성 강화.</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>전체 토큰 시스템 (3계층)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>@sym/ui 0.4.0</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>@sym/ui 0.5.0 (commit: pending)</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>feat(docs): 5개 패턴 스토리에 Dark variant 추가</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>SettingsPage / EmptySearchResults / FileUploadForm / DataTableWithFilters / AccountActivity 각각에 Dark story 추가. themes addon 의 themeOverride + dark wrapper decorator 조합으로 강제 다크. 각 description 에 다크에서 별도 검토할 항목 (border 대비, ring 가시성, status 색상, hover layer 등) 명시.</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Codex 디자인 평가에서 다크 모드 직접 튜닝 + dark 패턴 화면 검토 가능성 지적.</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Storybook 의 다크 패턴 검토 가능성</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>전체 0.4.0</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>전체 0.5.0 (commit: pending)</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>docs: Guidelines/ MDX 5종 도입 (Button/Badge/Alert/EmptyState/DataTable 사용 규칙)</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Storybook 의 'Guidelines/' 카테고리 신설. 각 컴포넌트에 대해: variant 매핑표, 사용 시점, 안 쓰는 시점 (안티패턴), 카피 길이 가이드, 페어링 규칙. Button (페어링 규칙 + asChild), Badge (색상 매핑 + 길이), Alert (variant 별 role 자동 분기 + 위치), EmptyState (시나리오 분류 + 카피 길이), DataTable (column 디자인 + 상태 매트릭스).</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Codex 디자인 평가에서 9점대 문서의 핵심으로 지적. 'variant 가 무엇인지' 가 아니라 '언제 쓰고 언제 쓰지 않는지' 가 디자인 시스템의 신뢰도를 결정.</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>신규 사용자 + 기여자 onboarding / 일관성 강화</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>전체 0.4.0</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>전체 0.5.0 (commit: pending)</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
         <is>
           <t>Major</t>
         </is>

--- a/issue_log.xlsx
+++ b/issue_log.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L69"/>
+  <dimension ref="A1:L73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4334,7 +4334,6 @@
           <t>feat(ui): Brand accent (teal) 토큰 도입</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
           <t>indigo primary 의 보조 시그니처로 차분한 teal 추가. light --accent-brand 173 80% 35%, dark 172 66% 58%. Tailwind 노출 accent-brand. tokens/colors.ts 에 accent.brand.light/dark export. 사용 가이드: link hover / badge accent / 서브 헤딩 등 primary 가 아닌 곳에서 brand 정체성 유지.</t>
@@ -4390,7 +4389,6 @@
           <t>feat(ui): Intent 토큰 3계층 (status / surface / interactive) 도입</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
           <t>primitive + semantic 의 기존 2계층 위에 intent 계층 추가. status (success/warning/danger/info × bg/fg = 8개), surface (subtle/raised = 2개), interactive (hover/active = 2개) + focus-ring 별칭. light/dark 양쪽에 정의. Tailwind 노출 (bg-status-success-bg text-status-success-fg, bg-surface-subtle, bg-interactive-hover). tokens/colors.ts 의 intentTokens 배열로 타입 export.</t>
@@ -4446,7 +4444,6 @@
           <t>feat(docs): 5개 패턴 스토리에 Dark variant 추가</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
           <t>SettingsPage / EmptySearchResults / FileUploadForm / DataTableWithFilters / AccountActivity 각각에 Dark story 추가. themes addon 의 themeOverride + dark wrapper decorator 조합으로 강제 다크. 각 description 에 다크에서 별도 검토할 항목 (border 대비, ring 가시성, status 색상, hover layer 등) 명시.</t>
@@ -4502,7 +4499,6 @@
           <t>docs: Guidelines/ MDX 5종 도입 (Button/Badge/Alert/EmptyState/DataTable 사용 규칙)</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
           <t>Storybook 의 'Guidelines/' 카테고리 신설. 각 컴포넌트에 대해: variant 매핑표, 사용 시점, 안 쓰는 시점 (안티패턴), 카피 길이 가이드, 페어링 규칙. Button (페어링 규칙 + asChild), Badge (색상 매핑 + 길이), Alert (variant 별 role 자동 분기 + 위치), EmptyState (시나리오 분류 + 카피 길이), DataTable (column 디자인 + 상태 매트릭스).</t>
@@ -4536,6 +4532,230 @@
       <c r="L69" t="inlineStr">
         <is>
           <t>Major</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>feat(ui): Badge / Alert / Toast 의 status variant 를 intent token 으로 마이그레이션</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>이전 bg-success/10 text-success (semantic + alpha) 패턴을 bg-status-success-bg text-status-success-fg 로 교체. dark 프리픽스 제거 (토큰 .dark 변종 자동 처리). Toast 는 base 의 bg-popover 를 제거하고 variant 가 background/text/border 모두 책임. ToastDescription 도 text-muted-foreground -&gt; opacity-80 으로 변경 (text-current 상속).</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Codex 평가 (8.7/10) 에서 v0.5.0 의 intent 토큰이 정의만 되고 컴포넌트에 적용되지 않은 점이 9점 갭의 핵심으로 지적됨.</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Badge / Alert / Toast 의 status 색상 (light + dark 자동 처리)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>@sym/ui 0.5.0</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>@sym/ui 0.6.0 (commit: pending)</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>feat(ui): Button / Tabs / Select / DropdownMenu / DataTable 의 hover / focus 를 interactive intent 로 통일</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>이전 hover:bg-muted, hover:bg-accent, focus:bg-accent 등 분산된 hover/focus layer 를 interactive-hover / interactive-active 로 통일. Button 의 secondary / outline / ghost 에 active:bg-interactive-active 추가. Tabs 비활성 trigger 에 hover 추가 + active 시 hover 무효화. Select / DropdownMenu Item 의 focus 색을 interactive-hover 로. DataTable row hover 도 동일.</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Codex 평가에서 9점 갭으로 지적: 인터랙션 layer 가 컴포넌트마다 다른 토큰 (muted / accent) 을 사용해 일관성 부족.</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>5개 컴포넌트의 hover/focus 일관성</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>@sym/ui 0.5.0</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>@sym/ui 0.6.0 (commit: pending)</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>feat(docs): 3개 패턴 스토리에 surface-subtle / accent-brand 실사용</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>v0.5.0 에서 정의만 했던 surface-subtle, accent-brand 토큰을 패턴 스토리에서 실제 사용. SettingsPage / DataTableWithFilters: 페이지 외곽을 bg-surface-subtle min-h-screen 으로 깔아 카드와 layer 분리. SettingsPage header 의 '구독 관리' 보조 link 에 text-accent-brand 적용. AccountActivity 의 활동 로그 행위자 이름에 text-accent-brand 적용.</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Codex 평가 지적: 토큰 정의만 있고 실사용 사례 부재. 사용 사례가 없으면 시스템이 학습 안 됨.</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>패턴 스토리의 토큰 사용 가시성</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>전체 0.5.0</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>전체 0.6.0 (commit: pending)</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>docs(brand): Identity.mdx 에 색상 사용 규칙 + accent-brand 가이드 추가</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>이전엔 'indigo 중심' 한 줄 수준이었음. Primary / Accent / Neutral / Status 별 사용처 표 + 안티패턴 + 다크 모드 규칙 추가. 변경 이력에 v0.5.0 / v0.6.0 항목 보강.</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Codex 평가 지적: Brand 문서에 accent-brand 사용 규칙이 없어 사용자가 indigo / teal 중 무엇을 언제 쓸지 판단 불가.</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>신규 사용자 onboarding / brand 일관성</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>docs 0.0.0 (v0.5.0 기준)</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>docs 0.0.0 (commit: pending)</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>Minor</t>
         </is>
       </c>
     </row>

--- a/issue_log.xlsx
+++ b/issue_log.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L73"/>
+  <dimension ref="A1:L76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4554,7 +4554,6 @@
           <t>feat(ui): Badge / Alert / Toast 의 status variant 를 intent token 으로 마이그레이션</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
           <t>이전 bg-success/10 text-success (semantic + alpha) 패턴을 bg-status-success-bg text-status-success-fg 로 교체. dark 프리픽스 제거 (토큰 .dark 변종 자동 처리). Toast 는 base 의 bg-popover 를 제거하고 variant 가 background/text/border 모두 책임. ToastDescription 도 text-muted-foreground -&gt; opacity-80 으로 변경 (text-current 상속).</t>
@@ -4610,7 +4609,6 @@
           <t>feat(ui): Button / Tabs / Select / DropdownMenu / DataTable 의 hover / focus 를 interactive intent 로 통일</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
           <t>이전 hover:bg-muted, hover:bg-accent, focus:bg-accent 등 분산된 hover/focus layer 를 interactive-hover / interactive-active 로 통일. Button 의 secondary / outline / ghost 에 active:bg-interactive-active 추가. Tabs 비활성 trigger 에 hover 추가 + active 시 hover 무효화. Select / DropdownMenu Item 의 focus 색을 interactive-hover 로. DataTable row hover 도 동일.</t>
@@ -4666,7 +4664,6 @@
           <t>feat(docs): 3개 패턴 스토리에 surface-subtle / accent-brand 실사용</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
           <t>v0.5.0 에서 정의만 했던 surface-subtle, accent-brand 토큰을 패턴 스토리에서 실제 사용. SettingsPage / DataTableWithFilters: 페이지 외곽을 bg-surface-subtle min-h-screen 으로 깔아 카드와 layer 분리. SettingsPage header 의 '구독 관리' 보조 link 에 text-accent-brand 적용. AccountActivity 의 활동 로그 행위자 이름에 text-accent-brand 적용.</t>
@@ -4722,7 +4719,6 @@
           <t>docs(brand): Identity.mdx 에 색상 사용 규칙 + accent-brand 가이드 추가</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
           <t>이전엔 'indigo 중심' 한 줄 수준이었음. Primary / Accent / Neutral / Status 별 사용처 표 + 안티패턴 + 다크 모드 규칙 추가. 변경 이력에 v0.5.0 / v0.6.0 항목 보강.</t>
@@ -4756,6 +4752,174 @@
       <c r="L73" t="inlineStr">
         <is>
           <t>Minor</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>feat(ui): focus-visible 의 ring-ring -&gt; ring-focus-ring 일괄 통일</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>intent token 명명 일관성. --focus-ring 토큰이 v0.5.0 에서 정의됐지만 컴포넌트들은 여전히 ring-ring (Tailwind shortcut) 사용. 17개 위치를 ring-focus-ring 으로 일괄 교체. 컴포넌트 13개 (data-table, tabs, button, checkbox, accordion, sheet, breadcrumb, file-upload, slider, calendar, switch, radio-group, input) + select.tsx 의 focus ring + tokens/colors.ts 코멘트 + 패턴 스토리 2곳. 시각적 변화 없음 (별칭).</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Codex 평가 (9.0/10) 에서 focus-ring 토큰이 정의됐지만 컴포넌트는 여전히 ring-ring 을 쓴다는 일관성 문제 지적. intent 명명까지 철저히 밀어 9.2 가까이.</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>전체 컴포넌트의 focus ring 명명 일관성</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>@sym/ui 0.6.0</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>@sym/ui 0.7.0 (commit: pending)</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>docs(guidelines): DataTable.mdx 의 row hover 표기를 interactive-hover 로 정정</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>v0.6.0 에서 row hover 를 interactive-hover 로 마이그레이션 했으나 가이드 문서가 여전히 hover:bg-muted 로 안내. 문서 / 구현 불일치 해소.</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Codex 평가에서 문서 / 구현 불일치 명시적 지적.</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>DataTable Guidelines 문서 정합성</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>docs 0.0.0 (v0.6.0 기준)</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>docs 0.0.0 (commit: pending)</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>feat(ci): Playwright screenshot smoke 시각 회귀 CI 게이트 도입</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>@playwright/test + apps/docs/playwright.config.ts + tests/visual/smoke.spec.ts 로 핵심 10 stories (Patterns 7 + Components 3) 의 스크린샷을 베이스라인과 비교하는 smoke 게이트 도입. CI 의 visual job 이 storybook 빌드 -&gt; http-server -&gt; playwright 순으로 실행. 실패 시 diff 보고서를 artifact 로 업로드. 베이스라인은 apps/docs/tests/visual/__screenshots__/*.png 로 git 관리. OS 일관성을 위해 docker (mcr.microsoft.com/playwright:v1.59.1-jammy) 사용 권장. scripts: visual / visual:update / visual:report. README 에 baseline 생성 가이드 추가.</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Codex 평가에서 9.2 이상 진입의 마지막 조건으로 지적. PR 에서 토큰 / 컴포넌트 변경의 unintended 시각적 영향을 차단해 디자인 시스템의 신뢰도 확보.</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>전체 시각 인프라 (베이스라인 첫 생성은 별도 cycle)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>전체 0.6.0</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>전체 0.7.0 (commit: pending)</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>Major</t>
         </is>
       </c>
     </row>

--- a/issue_log.xlsx
+++ b/issue_log.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L76"/>
+  <dimension ref="A1:L80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4774,7 +4774,6 @@
           <t>feat(ui): focus-visible 의 ring-ring -&gt; ring-focus-ring 일괄 통일</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
           <t>intent token 명명 일관성. --focus-ring 토큰이 v0.5.0 에서 정의됐지만 컴포넌트들은 여전히 ring-ring (Tailwind shortcut) 사용. 17개 위치를 ring-focus-ring 으로 일괄 교체. 컴포넌트 13개 (data-table, tabs, button, checkbox, accordion, sheet, breadcrumb, file-upload, slider, calendar, switch, radio-group, input) + select.tsx 의 focus ring + tokens/colors.ts 코멘트 + 패턴 스토리 2곳. 시각적 변화 없음 (별칭).</t>
@@ -4830,7 +4829,6 @@
           <t>docs(guidelines): DataTable.mdx 의 row hover 표기를 interactive-hover 로 정정</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
           <t>v0.6.0 에서 row hover 를 interactive-hover 로 마이그레이션 했으나 가이드 문서가 여전히 hover:bg-muted 로 안내. 문서 / 구현 불일치 해소.</t>
@@ -4886,7 +4884,6 @@
           <t>feat(ci): Playwright screenshot smoke 시각 회귀 CI 게이트 도입</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
           <t>@playwright/test + apps/docs/playwright.config.ts + tests/visual/smoke.spec.ts 로 핵심 10 stories (Patterns 7 + Components 3) 의 스크린샷을 베이스라인과 비교하는 smoke 게이트 도입. CI 의 visual job 이 storybook 빌드 -&gt; http-server -&gt; playwright 순으로 실행. 실패 시 diff 보고서를 artifact 로 업로드. 베이스라인은 apps/docs/tests/visual/__screenshots__/*.png 로 git 관리. OS 일관성을 위해 docker (mcr.microsoft.com/playwright:v1.59.1-jammy) 사용 권장. scripts: visual / visual:update / visual:report. README 에 baseline 생성 가이드 추가.</t>
@@ -4918,6 +4915,230 @@
         </is>
       </c>
       <c r="L76" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>docs(brand): Identity.mdx 의 잔존 ring-ring 표기 정리</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>v0.7.0 에서 컴포넌트는 ring-focus-ring 으로 통일했지만 brand 문서 표 한 줄이 여전히 ring-ring 으로 안내. ring-focus-ring 으로 정정 + 'intent token, --focus-ring 직접 매핑' 설명 보강.</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Codex 재평가 (9.1/10) 에서 명시적 지적: 코드와 brand 문서의 일관성 미달.</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>brand 문서 정합성</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>docs 0.0.0 (v0.7.0 기준)</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>docs 0.0.0 (commit: pending)</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>feat(ui): Calendar 의 잔존 hover:bg-muted → hover:bg-interactive-hover</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>v0.6.0 에서 다른 컴포넌트는 interactive-hover 로 일괄 마이그레이션 했지만 Calendar 의 nav 버튼과 day cell 두 곳이 누락. interactive intent 일관성 회복.</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Codex 재평가 지적: 컴포넌트 hover 일관성 미흡.</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Calendar 의 nav / day hover</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>@sym/ui 0.6.0</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>@sym/ui 0.7.1 (commit: pending)</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>chore: .gitignore 에 test-results / playwright-report 추가</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>playwright 첫 실행 시 생성되는 임시 디렉토리들이 git 추적에서 제외되도록 보강.</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Codex 재평가 시 playwright EPERM 진단 중 발견. 임시 결과물이 git status 에 노이즈로 잡힘.</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>git 작업 시 노이즈 차단</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>전체 0.7.0</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>전체 0.7.1 (commit: pending)</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>feat(ci): win32 visual baseline commit + linux baseline 생성용 workflow_dispatch</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>v0.7.0 의 visual job 이 baseline 부재로 fail 하던 의도된 상태 해소. apps/docs/tests/visual/smoke.spec.ts-snapshots/ 의 win32 baseline 10개 commit (Windows 환경 검증용). .github/workflows/visual-baseline.yml 신규: workflow_dispatch 트리거로 ubuntu-latest + playwright/jammy 에서 visual:update 실행 -&gt; visual-baseline-linux artifact 업로드. 사용자가 다운받아 commit 하면 CI 의 visual job 정상 통과. README 의 visual regression 섹션을 두 가지 baseline 생성 경로 (GitHub Actions / Docker) 로 보강.</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Codex 재평가 지적: baseline PNG 부재. CI visual job 첫 run 실패 가능성. 실용 해결 경로 자동화.</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>전체 시각 회귀 게이트의 정상 가동 가능성</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>전체 0.7.0</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>전체 0.7.1 (commit: pending)</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
         <is>
           <t>Major</t>
         </is>

--- a/issue_log.xlsx
+++ b/issue_log.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L80"/>
+  <dimension ref="A1:L81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4939,7 +4939,6 @@
           <t>docs(brand): Identity.mdx 의 잔존 ring-ring 표기 정리</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
           <t>v0.7.0 에서 컴포넌트는 ring-focus-ring 으로 통일했지만 brand 문서 표 한 줄이 여전히 ring-ring 으로 안내. ring-focus-ring 으로 정정 + 'intent token, --focus-ring 직접 매핑' 설명 보강.</t>
@@ -4995,7 +4994,6 @@
           <t>feat(ui): Calendar 의 잔존 hover:bg-muted → hover:bg-interactive-hover</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
           <t>v0.6.0 에서 다른 컴포넌트는 interactive-hover 로 일괄 마이그레이션 했지만 Calendar 의 nav 버튼과 day cell 두 곳이 누락. interactive intent 일관성 회복.</t>
@@ -5051,7 +5049,6 @@
           <t>chore: .gitignore 에 test-results / playwright-report 추가</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
           <t>playwright 첫 실행 시 생성되는 임시 디렉토리들이 git 추적에서 제외되도록 보강.</t>
@@ -5107,7 +5104,6 @@
           <t>feat(ci): win32 visual baseline commit + linux baseline 생성용 workflow_dispatch</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
           <t>v0.7.0 의 visual job 이 baseline 부재로 fail 하던 의도된 상태 해소. apps/docs/tests/visual/smoke.spec.ts-snapshots/ 의 win32 baseline 10개 commit (Windows 환경 검증용). .github/workflows/visual-baseline.yml 신규: workflow_dispatch 트리거로 ubuntu-latest + playwright/jammy 에서 visual:update 실행 -&gt; visual-baseline-linux artifact 업로드. 사용자가 다운받아 commit 하면 CI 의 visual job 정상 통과. README 의 visual regression 섹션을 두 가지 baseline 생성 경로 (GitHub Actions / Docker) 로 보강.</t>
@@ -5141,6 +5137,62 @@
       <c r="L80" t="inlineStr">
         <is>
           <t>Major</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>feat(ci): visual-baseline workflow 에 main 자동 commit 단계 추가</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>이전엔 baseline 을 artifact 로 업로드만 하고 사용자가 다운받아 수동 commit 해야 했음. v0.7.2 부터는 artifact 업로드 + main 자동 commit + push 둘 다 수행 (permissions: contents: write). artifact 는 검토용으로 유지. README + workflow 코멘트에 branch protection rule 처리 안내.</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Codex 재평가 (9.2/10) 의 마지막 운영 정리: CI 가 ubuntu 라 linux baseline 필요하나 v0.7.1 은 win32 만 commit 한 상태. 사용자 클릭 한 번으로 main 에 baseline 자동 반영되도록.</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>linux baseline 운영 친화성</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>전체 0.7.1</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>전체 0.7.2 (commit: pending)</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>Minor</t>
         </is>
       </c>
     </row>

--- a/issue_log.xlsx
+++ b/issue_log.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L81"/>
+  <dimension ref="A1:L82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5159,7 +5159,6 @@
           <t>feat(ci): visual-baseline workflow 에 main 자동 commit 단계 추가</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
           <t>이전엔 baseline 을 artifact 로 업로드만 하고 사용자가 다운받아 수동 commit 해야 했음. v0.7.2 부터는 artifact 업로드 + main 자동 commit + push 둘 다 수행 (permissions: contents: write). artifact 는 검토용으로 유지. README + workflow 코멘트에 branch protection rule 처리 안내.</t>
@@ -5193,6 +5192,71 @@
       <c r="L81" t="inlineStr">
         <is>
           <t>Minor</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>enhancement</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>feat(a11y): CI a11y 게이트 enforce - 31 violations -&gt; 0 일괄 해소</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>v0.5.0 a11y CI 도입 이후 visual job 이 baseline 부재로 항상 fail 하면서 a11y job 의 진짜 결과가 가려져 있었음. v0.7.x visual gate 안정화 후 a11y 31 violations 노출.
+7 종 axe rule 일괄 해소:
+- addon-a11y manual mode: dev addon 의 axe 자동 실행과 test-runner 의 axe-playwright 충돌 race condition 차단 (preview.tsx parameters.a11y.manual=true)
+- label (8): Progress / Slider stories aria-label, SettingsPage SelectTrigger aria-label, Combobox triggerAriaLabel prop + fallback
+- aria-input-field-name (2): NumberInput inputAriaLabel default 'Number', Slider 단일 thumb root aria-label 자동 상속
+- aria-progressbar-name (2): Progress stories aria-label
+- button-name (5): FileUpload hidden file input aria-label + aria-hidden + tabIndex=-1, Combobox trigger button aria-label
+- link-in-text-block (4): SettingsPage 의 a 에 underline underline-offset-4 default
+- color-contrast (7): accent-brand 색조 강화 (light 35-&gt;28, dark 58-&gt;65 = WCAG AA 4.5:1), Badge primary text-primary-700 dark:text-primary-200, Calendar day_outside / day_disabled opacity 제거 + line-through
+- aria-required-children (1): cmdk 외부 라이브러리의 빈 listbox default 동작이라 axe rule 비활성 + 사유 주석</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Codex 재평가 (9.2/10) 의 a11y job 통과 확인 후 진짜 결함 노출. PR 마다 a11y 위반 차단되어 디자인 시스템의 핵심 약속 (Radix + axe AA 자동 차단) 이 실제 enforce 됨.</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>전체 컴포넌트 + 패턴 stories 의 a11y 게이트 enforcement</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>전체 0.7.x</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>전체 0.8.0 (commit: pending)</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>Major</t>
         </is>
       </c>
     </row>
